--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6261968-BAD6-49CB-AF15-548F8062DA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFC4F62-7D6B-4D7A-9ED9-1A3D83F88C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="314">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -986,6 +986,9 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهور سبتمبر - اكتوبر- نوفمبر - ديسمبر / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر يوليه واغسطس /2026</t>
   </si>
 </sst>
 </file>
@@ -5545,7 +5548,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -5751,10 +5754,12 @@
       <c r="B12" s="8">
         <v>7</v>
       </c>
-      <c r="C12" s="77">
-        <v>46232</v>
-      </c>
-      <c r="D12" s="33"/>
+      <c r="C12" s="98">
+        <v>46270</v>
+      </c>
+      <c r="D12" s="33">
+        <v>300</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="33">
         <v>300</v>
@@ -5776,10 +5781,12 @@
       <c r="B13" s="8">
         <v>8</v>
       </c>
-      <c r="C13" s="77">
-        <v>46354</v>
-      </c>
-      <c r="D13" s="33"/>
+      <c r="C13" s="98">
+        <v>46270</v>
+      </c>
+      <c r="D13" s="33">
+        <v>300</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="33">
         <v>300</v>
@@ -11612,7 +11619,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>17875</v>
+        <v>18475</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13316,12 +13323,22 @@
       <c r="A79" s="8">
         <v>75</v>
       </c>
-      <c r="B79" s="51"/>
-      <c r="C79" s="55"/>
+      <c r="B79" s="51">
+        <v>46270</v>
+      </c>
+      <c r="C79" s="55">
+        <v>600</v>
+      </c>
       <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
+      <c r="E79" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F79" s="8">
+        <v>8</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A80" s="8">
@@ -13536,15 +13553,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>17875</v>
+        <v>18475</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>20246</v>
+        <v>20296</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11531</v>
+        <v>12081</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13931,7 +13948,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>20246</v>
+        <v>20296</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14738,9 +14755,15 @@
       <c r="A46" s="33">
         <v>42</v>
       </c>
-      <c r="B46" s="60"/>
-      <c r="C46" s="55"/>
-      <c r="D46" s="8"/>
+      <c r="B46" s="60">
+        <v>46270</v>
+      </c>
+      <c r="C46" s="55">
+        <v>50</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="47" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
@@ -20801,7 +20824,7 @@
       </c>
       <c r="J12" s="26">
         <f>Apartment8!D12</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K12" s="26">
         <f>Apartment9!D12</f>
@@ -20863,7 +20886,7 @@
       </c>
       <c r="J13" s="26">
         <f>Apartment8!D13</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K13" s="26">
         <f>Apartment9!D13</f>
@@ -21634,12 +21657,12 @@
       </c>
       <c r="C12" s="91">
         <f>Apartment8!D4</f>
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="D12" s="92"/>
       <c r="E12" s="94">
         <f t="shared" si="0"/>
-        <v>-1800</v>
+        <v>-2400</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>120</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFC4F62-7D6B-4D7A-9ED9-1A3D83F88C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F371D0-6041-4D64-A55B-AB076F7A6706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="317">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -989,6 +989,15 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهر يوليه واغسطس /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر سبتمبر /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فاتورة المياه عن شهر سبتمبر /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة المجارى فى الجراج</t>
   </si>
 </sst>
 </file>
@@ -13557,11 +13566,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>20296</v>
+        <v>21646</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>12081</v>
+        <v>10731</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13948,7 +13957,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>20296</v>
+        <v>21646</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14769,33 +14778,57 @@
       <c r="A47" s="33">
         <v>43</v>
       </c>
-      <c r="B47" s="60"/>
-      <c r="C47" s="55"/>
-      <c r="D47" s="8"/>
+      <c r="B47" s="60">
+        <v>46282</v>
+      </c>
+      <c r="C47" s="55">
+        <v>298</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="48" spans="1:20" ht="18" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>44</v>
       </c>
-      <c r="B48" s="60"/>
-      <c r="C48" s="55"/>
-      <c r="D48" s="8"/>
+      <c r="B48" s="60">
+        <v>46282</v>
+      </c>
+      <c r="C48" s="55">
+        <v>2</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>45</v>
       </c>
-      <c r="B49" s="60"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="8"/>
+      <c r="B49" s="60">
+        <v>46282</v>
+      </c>
+      <c r="C49" s="55">
+        <v>1030</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>46</v>
       </c>
-      <c r="B50" s="60"/>
-      <c r="C50" s="55"/>
-      <c r="D50" s="8"/>
+      <c r="B50" s="60">
+        <v>46282</v>
+      </c>
+      <c r="C50" s="55">
+        <v>20</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A51" s="33">

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F371D0-6041-4D64-A55B-AB076F7A6706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A963B63-DAA0-42BB-BCFA-2E59FDC8F193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="318">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -998,6 +998,9 @@
   </si>
   <si>
     <t>تحت حساب نظافة المجارى فى الجراج</t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر سبتمبر /2026</t>
   </si>
 </sst>
 </file>
@@ -5557,7 +5560,7 @@
       <c r="C4" s="76"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -5818,9 +5821,11 @@
         <v>9</v>
       </c>
       <c r="C14" s="77">
-        <v>46354</v>
-      </c>
-      <c r="D14" s="33"/>
+        <v>46289</v>
+      </c>
+      <c r="D14" s="33">
+        <v>300</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="33">
         <v>300</v>
@@ -11628,7 +11633,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>18475</v>
+        <v>18775</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13353,12 +13358,22 @@
       <c r="A80" s="8">
         <v>76</v>
       </c>
-      <c r="B80" s="51"/>
-      <c r="C80" s="55"/>
+      <c r="B80" s="51">
+        <v>46289</v>
+      </c>
+      <c r="C80" s="55">
+        <v>300</v>
+      </c>
       <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
+      <c r="E80" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="F80" s="8">
+        <v>8</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="81" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A81" s="8">
@@ -13562,15 +13577,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>18475</v>
+        <v>18775</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>21646</v>
+        <v>22046</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10731</v>
+        <v>10631</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13957,7 +13972,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>21646</v>
+        <v>22046</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14834,9 +14849,15 @@
       <c r="A51" s="33">
         <v>47</v>
       </c>
-      <c r="B51" s="60"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="8"/>
+      <c r="B51" s="60">
+        <v>46297</v>
+      </c>
+      <c r="C51" s="55">
+        <v>400</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A52" s="33">
@@ -20981,7 +21002,7 @@
       </c>
       <c r="J14" s="26">
         <f>Apartment8!D14</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K14" s="26">
         <f>Apartment9!D14</f>
@@ -21690,12 +21711,12 @@
       </c>
       <c r="C12" s="91">
         <f>Apartment8!D4</f>
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="D12" s="92"/>
       <c r="E12" s="94">
         <f t="shared" si="0"/>
-        <v>-2400</v>
+        <v>-2700</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>120</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A963B63-DAA0-42BB-BCFA-2E59FDC8F193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0098B35-4E00-46DF-B772-0F143541A7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="12" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="321">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -1001,6 +1001,15 @@
   </si>
   <si>
     <t>تحت حساب نظافة السلم لام احمد عن شهر سبتمبر /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر سبتمبر / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807951149146700023 بتاريخ اصدار 21- ديسمبر - 2025 بفائدة 14%، عن شهر اكتوبر / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب فوائد شهادة  رقم 1807581149146700038 بتاريخ اصدار 4- يناير - 2026 بفائدة 19.25%، عن شهر اكتوبر / 2026</t>
   </si>
 </sst>
 </file>
@@ -11633,7 +11642,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>18775</v>
+        <v>19731</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13379,129 +13388,210 @@
       <c r="A81" s="8">
         <v>77</v>
       </c>
-      <c r="B81" s="51"/>
-      <c r="C81" s="55"/>
+      <c r="B81" s="51">
+        <v>46287</v>
+      </c>
+      <c r="C81" s="55">
+        <v>58</v>
+      </c>
       <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
+      <c r="E81" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
+      <c r="G81" s="8" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="82" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A82" s="8">
         <v>78</v>
       </c>
-      <c r="B82" s="51"/>
-      <c r="C82" s="55"/>
-      <c r="E82" s="8"/>
+      <c r="B82" s="51">
+        <v>46317</v>
+      </c>
+      <c r="C82" s="55">
+        <v>58</v>
+      </c>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
+      <c r="G82" s="8" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="83" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A83" s="8">
         <v>79</v>
       </c>
-      <c r="B83" s="51"/>
-      <c r="C83" s="55"/>
-      <c r="E83" s="8"/>
+      <c r="B83" s="51">
+        <v>46317</v>
+      </c>
+      <c r="C83" s="55">
+        <v>240</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>260</v>
+      </c>
       <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
+      <c r="G83" s="8" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A84" s="8">
         <v>80</v>
       </c>
+      <c r="B84" s="51">
+        <v>46317</v>
+      </c>
+      <c r="C84" s="55">
+        <v>300</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" s="8">
+        <v>7</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A85" s="8">
         <v>81</v>
       </c>
-      <c r="G85" s="8"/>
+      <c r="B85" s="51">
+        <v>46317</v>
+      </c>
+      <c r="C85" s="55">
+        <v>150</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F85" s="8">
+        <v>4</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="86" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A86" s="8">
         <v>82</v>
       </c>
-      <c r="G86" s="8"/>
+      <c r="B86" s="51">
+        <v>46317</v>
+      </c>
+      <c r="C86" s="55">
+        <v>150</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F86" s="8">
+        <v>3</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="87" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A87" s="8">
         <v>83</v>
       </c>
+      <c r="B87" s="51"/>
       <c r="G87" s="8"/>
     </row>
     <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
         <v>84</v>
       </c>
+      <c r="B88" s="51"/>
       <c r="G88" s="8"/>
     </row>
     <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>85</v>
       </c>
+      <c r="B89" s="51"/>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A90" s="8">
         <v>86</v>
       </c>
+      <c r="B90" s="51"/>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A91" s="8">
         <v>87</v>
       </c>
+      <c r="B91" s="51"/>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A92" s="8">
         <v>88</v>
       </c>
+      <c r="B92" s="51"/>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A93" s="8">
         <v>89</v>
       </c>
+      <c r="B93" s="51"/>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A94" s="8">
         <v>90</v>
       </c>
+      <c r="B94" s="51"/>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="B95" s="51"/>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="B96" s="51"/>
       <c r="G96" s="8"/>
     </row>
-    <row r="97" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="B97" s="51"/>
       <c r="G97" s="8"/>
     </row>
-    <row r="98" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G98" s="8"/>
     </row>
-    <row r="99" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G99" s="8"/>
     </row>
-    <row r="100" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G100" s="8"/>
     </row>
-    <row r="101" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G101" s="8"/>
     </row>
-    <row r="102" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G102" s="8"/>
     </row>
-    <row r="103" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G103" s="8"/>
     </row>
-    <row r="104" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G104" s="8"/>
     </row>
-    <row r="105" spans="7:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="G105" s="8"/>
     </row>
   </sheetData>
@@ -13577,15 +13667,15 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>18775</v>
+        <v>19731</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>22046</v>
+        <v>22921</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10631</v>
+        <v>10712</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -13972,7 +14062,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>22046</v>
+        <v>22921</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -14863,9 +14953,15 @@
       <c r="A52" s="33">
         <v>48</v>
       </c>
-      <c r="B52" s="60"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="8"/>
+      <c r="B52" s="60">
+        <v>46316</v>
+      </c>
+      <c r="C52" s="55">
+        <v>875</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A53" s="33">

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0098B35-4E00-46DF-B772-0F143541A7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E6B4F2-1278-4A51-9612-A1CE51D61EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="322">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -1010,6 +1010,9 @@
   </si>
   <si>
     <t>تحت حساب فوائد شهادة  رقم 1807581149146700038 بتاريخ اصدار 4- يناير - 2026 بفائدة 19.25%، عن شهر اكتوبر / 2026</t>
+  </si>
+  <si>
+    <t>تحت حساب صيانة شهر اغسطس و سبتمبر /2026</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1173,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,6 +1220,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -1317,7 +1326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1639,6 +1648,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6245,7 +6257,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="83">
@@ -6532,10 +6544,12 @@
       <c r="B15" s="33">
         <v>10</v>
       </c>
-      <c r="C15" s="51">
-        <v>45567</v>
-      </c>
-      <c r="D15" s="33"/>
+      <c r="C15" s="112">
+        <v>46317</v>
+      </c>
+      <c r="D15" s="33">
+        <v>300</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="33">
         <v>300</v>
@@ -8252,7 +8266,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -8539,10 +8553,12 @@
       <c r="B15" s="8">
         <v>10</v>
       </c>
-      <c r="C15" s="9">
-        <v>45567</v>
-      </c>
-      <c r="D15" s="8"/>
+      <c r="C15" s="112">
+        <v>46317</v>
+      </c>
+      <c r="D15" s="8">
+        <v>150</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
         <v>150</v>
@@ -8929,7 +8945,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -9216,10 +9232,12 @@
       <c r="B15" s="8">
         <v>10</v>
       </c>
-      <c r="C15" s="63">
-        <v>46297</v>
-      </c>
-      <c r="D15" s="8"/>
+      <c r="C15" s="112">
+        <v>46317</v>
+      </c>
+      <c r="D15" s="8">
+        <v>150</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
         <v>150</v>
@@ -10930,7 +10948,7 @@
       <c r="C4" s="10"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -11166,10 +11184,12 @@
       <c r="B13" s="73">
         <v>8</v>
       </c>
-      <c r="C13" s="51">
-        <v>46306</v>
-      </c>
-      <c r="D13" s="73"/>
+      <c r="C13" s="98">
+        <v>46321</v>
+      </c>
+      <c r="D13" s="73">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="73">
         <v>150</v>
@@ -11191,10 +11211,12 @@
       <c r="B14" s="73">
         <v>9</v>
       </c>
-      <c r="C14" s="77">
-        <v>46306</v>
-      </c>
-      <c r="D14" s="73"/>
+      <c r="C14" s="98">
+        <v>46321</v>
+      </c>
+      <c r="D14" s="73">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="73">
         <v>150</v>
@@ -11642,7 +11664,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>19731</v>
+        <v>20031</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13506,8 +13528,22 @@
       <c r="A87" s="8">
         <v>83</v>
       </c>
-      <c r="B87" s="51"/>
-      <c r="G87" s="8"/>
+      <c r="B87" s="51">
+        <v>46321</v>
+      </c>
+      <c r="C87" s="55">
+        <v>300</v>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="8">
+        <v>1</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A88" s="8">
@@ -13667,7 +13703,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>19731</v>
+        <v>20031</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13675,7 +13711,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>10712</v>
+        <v>11012</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -21008,7 +21044,7 @@
       </c>
       <c r="C13" s="26">
         <f>Apartment1!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D13" s="26">
         <f>Apartment2!D13</f>
@@ -21070,7 +21106,7 @@
       </c>
       <c r="C14" s="26">
         <f>Apartment1!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D14" s="26">
         <f>Apartment2!D14</f>
@@ -21140,11 +21176,11 @@
       </c>
       <c r="E15" s="26">
         <f>Apartment3!D15</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F15" s="26">
         <f>Apartment4!D15</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G15" s="26">
         <f>Apartment5!D15</f>
@@ -21156,7 +21192,7 @@
       </c>
       <c r="I15" s="26">
         <f>Apartment7!D15</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="26">
         <f>Apartment8!D15</f>
@@ -21619,12 +21655,12 @@
       </c>
       <c r="C5" s="91">
         <f>Apartment1!D4</f>
-        <v>1050</v>
+        <v>1350</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="94">
         <f>D5-C5</f>
-        <v>-1050</v>
+        <v>-1350</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>50</v>
@@ -21673,12 +21709,12 @@
       </c>
       <c r="C7" s="91">
         <f>Apartment3!D4</f>
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D7" s="92"/>
       <c r="E7" s="94">
         <f t="shared" si="0"/>
-        <v>-1350</v>
+        <v>-1500</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -21700,12 +21736,12 @@
       </c>
       <c r="C8" s="91">
         <f>Apartment4!D4</f>
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="D8" s="92"/>
       <c r="E8" s="94">
         <f t="shared" si="0"/>
-        <v>-1350</v>
+        <v>-1500</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -21780,12 +21816,12 @@
       </c>
       <c r="C11" s="91">
         <f>Apartment7!D4</f>
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="D11" s="92"/>
       <c r="E11" s="94">
         <f t="shared" si="0"/>
-        <v>-2700</v>
+        <v>-3000</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E6B4F2-1278-4A51-9612-A1CE51D61EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDE94B-8B79-432A-B32D-78B307ED3EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="323">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>تحت حساب صيانة شهر اغسطس و سبتمبر /2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تحت حساب صيانة شهور 6، 7، 8، 9، 10  / 2026 </t>
   </si>
 </sst>
 </file>
@@ -1610,17 +1613,20 @@
     <xf numFmtId="164" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="2"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1648,9 +1654,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2677,23 +2680,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -3382,23 +3385,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -4055,23 +4058,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -4737,23 +4740,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:22" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="57"/>
@@ -4772,16 +4775,16 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="100" t="s">
+      <c r="O3" s="102" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="100"/>
-      <c r="Q3" s="100"/>
-      <c r="R3" s="100"/>
-      <c r="S3" s="100"/>
-      <c r="T3" s="100"/>
-      <c r="U3" s="100"/>
-      <c r="V3" s="100"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="102"/>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
     </row>
     <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="C4" s="49"/>
@@ -4831,12 +4834,12 @@
       <c r="Q5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="R5" s="106" t="s">
+      <c r="R5" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="S5" s="107"/>
-      <c r="T5" s="107"/>
-      <c r="U5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="109"/>
     </row>
     <row r="6" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -5075,10 +5078,10 @@
         <f>SUM(Q6:Q11)</f>
         <v>0</v>
       </c>
-      <c r="R12" s="109"/>
-      <c r="S12" s="110"/>
-      <c r="T12" s="110"/>
-      <c r="U12" s="111"/>
+      <c r="R12" s="110"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="112"/>
     </row>
     <row r="13" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -5538,23 +5541,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -6214,23 +6217,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="57"/>
@@ -6544,7 +6547,7 @@
       <c r="B15" s="33">
         <v>10</v>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="99">
         <v>46317</v>
       </c>
       <c r="D15" s="33">
@@ -6892,23 +6895,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -7576,23 +7579,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>116</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -8223,23 +8226,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -8553,7 +8556,7 @@
       <c r="B15" s="8">
         <v>10</v>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="99">
         <v>46317</v>
       </c>
       <c r="D15" s="8">
@@ -8902,23 +8905,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -9232,7 +9235,7 @@
       <c r="B15" s="8">
         <v>10</v>
       </c>
-      <c r="C15" s="112">
+      <c r="C15" s="99">
         <v>46317</v>
       </c>
       <c r="D15" s="8">
@@ -9581,23 +9584,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -10264,38 +10267,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="102" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="103" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -10905,23 +10908,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -11664,7 +11667,7 @@
       </c>
       <c r="C4" s="53">
         <f>SUM(C6:C2000)</f>
-        <v>20031</v>
+        <v>21531</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.2">
@@ -13549,14 +13552,28 @@
       <c r="A88" s="8">
         <v>84</v>
       </c>
-      <c r="B88" s="51"/>
-      <c r="G88" s="8"/>
+      <c r="B88" s="51">
+        <v>46321</v>
+      </c>
+      <c r="C88" s="55">
+        <v>1500</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="A89" s="8">
         <v>85</v>
       </c>
       <c r="B89" s="51"/>
+      <c r="C89" s="55"/>
       <c r="G89" s="8"/>
     </row>
     <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -13564,6 +13581,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="51"/>
+      <c r="C90" s="55"/>
       <c r="G90" s="8"/>
     </row>
     <row r="91" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -13571,6 +13589,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="51"/>
+      <c r="C91" s="55"/>
       <c r="G91" s="8"/>
     </row>
     <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -13578,6 +13597,7 @@
         <v>88</v>
       </c>
       <c r="B92" s="51"/>
+      <c r="C92" s="55"/>
       <c r="G92" s="8"/>
     </row>
     <row r="93" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -13585,6 +13605,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="51"/>
+      <c r="C93" s="55"/>
       <c r="G93" s="8"/>
     </row>
     <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.25">
@@ -13592,27 +13613,34 @@
         <v>90</v>
       </c>
       <c r="B94" s="51"/>
+      <c r="C94" s="55"/>
       <c r="G94" s="8"/>
     </row>
     <row r="95" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B95" s="51"/>
+      <c r="C95" s="55"/>
       <c r="G95" s="8"/>
     </row>
     <row r="96" spans="1:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B96" s="51"/>
+      <c r="C96" s="55"/>
       <c r="G96" s="8"/>
     </row>
     <row r="97" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B97" s="51"/>
+      <c r="C97" s="55"/>
       <c r="G97" s="8"/>
     </row>
     <row r="98" spans="2:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="C98" s="55"/>
       <c r="G98" s="8"/>
     </row>
     <row r="99" spans="2:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="C99" s="55"/>
       <c r="G99" s="8"/>
     </row>
     <row r="100" spans="2:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="C100" s="55"/>
       <c r="G100" s="8"/>
     </row>
     <row r="101" spans="2:7" ht="18" x14ac:dyDescent="0.25">
@@ -13652,21 +13680,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="45" t="s">
@@ -13703,7 +13731,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="70">
         <f>incomes!C4</f>
-        <v>20031</v>
+        <v>21531</v>
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
@@ -13711,7 +13739,7 @@
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>11012</v>
+        <v>12512</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -14076,21 +14104,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:19" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
     </row>
     <row r="3" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="58" t="s">
@@ -15623,38 +15651,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="102" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="103" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
+      <c r="G3" s="103"/>
+      <c r="H3" s="103"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="103"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="103"/>
+      <c r="M3" s="103"/>
+      <c r="N3" s="103"/>
+      <c r="O3" s="103"/>
+      <c r="P3" s="103"/>
+      <c r="Q3" s="103"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -16179,38 +16207,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:32" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="99"/>
-      <c r="AB2" s="99"/>
-      <c r="AC2" s="99"/>
-      <c r="AD2" s="99"/>
-      <c r="AE2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
+      <c r="R2" s="100"/>
+      <c r="S2" s="100"/>
+      <c r="T2" s="100"/>
+      <c r="U2" s="100"/>
+      <c r="V2" s="100"/>
+      <c r="W2" s="100"/>
+      <c r="X2" s="100"/>
+      <c r="Y2" s="100"/>
+      <c r="Z2" s="100"/>
+      <c r="AA2" s="100"/>
+      <c r="AB2" s="100"/>
+      <c r="AC2" s="100"/>
+      <c r="AD2" s="100"/>
+      <c r="AE2" s="100"/>
     </row>
     <row r="3" spans="1:32" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="10"/>
@@ -20502,37 +20530,37 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B3" s="3"/>
@@ -20968,11 +20996,11 @@
       </c>
       <c r="O11" s="26">
         <f>Apartment13!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P11" s="26">
         <f>Apartment14!D11</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -21030,11 +21058,11 @@
       </c>
       <c r="O12" s="26">
         <f>Apartment13!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P12" s="26">
         <f>Apartment14!D12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -21092,11 +21120,11 @@
       </c>
       <c r="O13" s="26">
         <f>Apartment13!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P13" s="26">
         <f>Apartment14!D13</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -21154,11 +21182,11 @@
       </c>
       <c r="O14" s="26">
         <f>Apartment13!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P14" s="26">
         <f>Apartment14!D14</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -21216,11 +21244,11 @@
       </c>
       <c r="O15" s="26">
         <f>Apartment13!D15</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P15" s="26">
         <f>Apartment14!D15</f>
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
@@ -21593,28 +21621,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
     </row>
     <row r="3" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="G3" s="103" t="s">
+      <c r="G3" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
     </row>
     <row r="4" spans="1:14" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -21974,12 +22002,12 @@
       </c>
       <c r="C17" s="91">
         <f>Apartment13!D4</f>
-        <v>675</v>
+        <v>1425</v>
       </c>
       <c r="D17" s="92"/>
       <c r="E17" s="94">
         <f t="shared" si="0"/>
-        <v>-675</v>
+        <v>-1425</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>56</v>
@@ -22001,12 +22029,12 @@
       </c>
       <c r="C18" s="91">
         <f>Apartment14!D4</f>
-        <v>675</v>
+        <v>1425</v>
       </c>
       <c r="D18" s="92"/>
       <c r="E18" s="94">
         <f t="shared" si="0"/>
-        <v>-675</v>
+        <v>-1425</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>57</v>
@@ -22224,23 +22252,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="1"/>
@@ -22267,7 +22295,7 @@
       <c r="C4" s="62"/>
       <c r="D4" s="11">
         <f>SUM(D6:D2001)</f>
-        <v>675</v>
+        <v>1425</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -22449,7 +22477,9 @@
       <c r="C11" s="63">
         <v>46242</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="33">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
         <v>150</v>
@@ -22474,7 +22504,9 @@
       <c r="C12" s="63">
         <v>46242</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="33">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>150</v>
@@ -22499,7 +22531,9 @@
       <c r="C13" s="51">
         <v>46371</v>
       </c>
-      <c r="D13" s="33"/>
+      <c r="D13" s="33">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
         <v>150</v>
@@ -22524,7 +22558,9 @@
       <c r="C14" s="51">
         <v>46371</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="33">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
         <v>150</v>
@@ -22549,7 +22585,9 @@
       <c r="C15" s="51">
         <v>46371</v>
       </c>
-      <c r="D15" s="33"/>
+      <c r="D15" s="33">
+        <v>150</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
         <v>150</v>
@@ -22893,23 +22931,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="75"/>
@@ -23560,23 +23598,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="C2" s="99" t="s">
+      <c r="C2" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="100"/>
+      <c r="Q2" s="100"/>
     </row>
     <row r="3" spans="1:17" ht="56.25" x14ac:dyDescent="0.4">
       <c r="C3" s="57"/>
@@ -23603,7 +23641,7 @@
       <c r="C4" s="49"/>
       <c r="D4" s="83">
         <f>SUM(D6:D2001)</f>
-        <v>675</v>
+        <v>1425</v>
       </c>
       <c r="E4" s="11"/>
       <c r="F4" s="11">
@@ -23785,7 +23823,9 @@
       <c r="C11" s="51">
         <v>46242</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="33">
+        <v>150</v>
+      </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
         <v>150</v>
@@ -23810,7 +23850,9 @@
       <c r="C12" s="51">
         <v>46242</v>
       </c>
-      <c r="D12" s="33"/>
+      <c r="D12" s="33">
+        <v>150</v>
+      </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8">
         <v>150</v>
@@ -23835,7 +23877,9 @@
       <c r="C13" s="51">
         <v>46371</v>
       </c>
-      <c r="D13" s="33"/>
+      <c r="D13" s="33">
+        <v>150</v>
+      </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8">
         <v>150</v>
@@ -23860,7 +23904,9 @@
       <c r="C14" s="51">
         <v>46371</v>
       </c>
-      <c r="D14" s="33"/>
+      <c r="D14" s="33">
+        <v>150</v>
+      </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8">
         <v>150</v>
@@ -23885,7 +23931,9 @@
       <c r="C15" s="51">
         <v>46371</v>
       </c>
-      <c r="D15" s="33"/>
+      <c r="D15" s="33">
+        <v>150</v>
+      </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8">
         <v>150</v>
@@ -23989,14 +24037,14 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="104" t="s">
+      <c r="I20" s="105" t="s">
         <v>118</v>
       </c>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="105"/>
     </row>
     <row r="21" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A21" s="8"/>
@@ -24007,14 +24055,14 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="104" t="s">
+      <c r="I21" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="J21" s="104"/>
-      <c r="K21" s="104"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="104"/>
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="105"/>
+      <c r="M21" s="105"/>
+      <c r="N21" s="105"/>
     </row>
     <row r="22" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
@@ -24052,13 +24100,13 @@
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
       <c r="I23" s="48"/>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="105"/>
-      <c r="M23" s="105"/>
-      <c r="N23" s="105"/>
-      <c r="O23" s="105"/>
-      <c r="P23" s="105"/>
+      <c r="J23" s="106"/>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="106"/>
+      <c r="N23" s="106"/>
+      <c r="O23" s="106"/>
+      <c r="P23" s="106"/>
     </row>
     <row r="24" spans="1:17" ht="18" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
@@ -24072,13 +24120,13 @@
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="105"/>
-      <c r="P24" s="105"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="106"/>
     </row>
     <row r="25" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
@@ -24092,13 +24140,13 @@
       </c>
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="105"/>
-      <c r="P25" s="105"/>
+      <c r="J25" s="106"/>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="106"/>
+      <c r="O25" s="106"/>
+      <c r="P25" s="106"/>
     </row>
     <row r="26" spans="1:17" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A26" s="8"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03EDE94B-8B79-432A-B32D-78B307ED3EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABE2D1F-B9F4-43AD-BF8A-942DDCAB4CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="monthly_elctricity" sheetId="28" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="324">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -1016,6 +1016,9 @@
   </si>
   <si>
     <t xml:space="preserve">تحت حساب صيانة شهور 6، 7، 8، 9، 10  / 2026 </t>
+  </si>
+  <si>
+    <t>تحت حساب نظافة السلم لام احمد عن شهر اكتوبر /2026</t>
   </si>
 </sst>
 </file>
@@ -1619,14 +1622,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4775,16 +4778,16 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-      <c r="O3" s="102" t="s">
+      <c r="O3" s="101" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="102"/>
-      <c r="S3" s="102"/>
-      <c r="T3" s="102"/>
-      <c r="U3" s="102"/>
-      <c r="V3" s="102"/>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="101"/>
+      <c r="R3" s="101"/>
+      <c r="S3" s="101"/>
+      <c r="T3" s="101"/>
+      <c r="U3" s="101"/>
+      <c r="V3" s="101"/>
     </row>
     <row r="4" spans="1:22" ht="18" x14ac:dyDescent="0.25">
       <c r="C4" s="49"/>
@@ -10267,38 +10270,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="102" t="s">
+      <c r="C2" s="101" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="103" t="s">
+      <c r="F3" s="102" t="s">
         <v>236</v>
       </c>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -13735,11 +13738,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>22921</v>
+        <v>23371</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>12512</v>
+        <v>12062</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -14126,7 +14129,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>22921</v>
+        <v>23371</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -15031,17 +15034,29 @@
       <c r="A53" s="33">
         <v>49</v>
       </c>
-      <c r="B53" s="60"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="8"/>
+      <c r="B53" s="60">
+        <v>46203</v>
+      </c>
+      <c r="C53" s="55">
+        <v>400</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>50</v>
       </c>
-      <c r="B54" s="60"/>
-      <c r="C54" s="55"/>
-      <c r="D54" s="8"/>
+      <c r="B54" s="60">
+        <v>46203</v>
+      </c>
+      <c r="C54" s="55">
+        <v>50</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
@@ -15651,38 +15666,38 @@
   <sheetData>
     <row r="1" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C2" s="102" t="s">
+      <c r="C2" s="101" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="1:17" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C3" s="83"/>
-      <c r="F3" s="103" t="s">
+      <c r="F3" s="102" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="103"/>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="103"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
     </row>
     <row r="4" spans="1:17" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
@@ -20530,21 +20545,21 @@
   <sheetData>
     <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B1" s="18"/>
-      <c r="C1" s="101" t="s">
+      <c r="C1" s="103" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
     </row>
     <row r="2" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="18"/>

--- a/Book2026.xlsx
+++ b/Book2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\syana05012019\2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABE2D1F-B9F4-43AD-BF8A-942DDCAB4CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBAA1C9B-3EB5-49F0-94B2-1A3D2A804D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="947" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="325">
   <si>
     <t>صفحة الإيرادات</t>
   </si>
@@ -1019,6 +1019,9 @@
   </si>
   <si>
     <t>تحت حساب نظافة السلم لام احمد عن شهر اكتوبر /2026</t>
+  </si>
+  <si>
+    <t>تحت حساب كهرباء شهر اكتوبر /2026</t>
   </si>
 </sst>
 </file>
@@ -13738,11 +13741,11 @@
       </c>
       <c r="D5" s="71">
         <f>outcomes!C3</f>
-        <v>23371</v>
+        <v>23691</v>
       </c>
       <c r="E5" s="72">
         <f>(C3+C5)-D5</f>
-        <v>12062</v>
+        <v>11742</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -14129,7 +14132,7 @@
       </c>
       <c r="C3" s="53">
         <f>SUM(C5:C2002)</f>
-        <v>23371</v>
+        <v>23691</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="36" x14ac:dyDescent="0.2">
@@ -15062,9 +15065,15 @@
       <c r="A55" s="33">
         <v>51</v>
       </c>
-      <c r="B55" s="60"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="8"/>
+      <c r="B55" s="60">
+        <v>46324</v>
+      </c>
+      <c r="C55" s="55">
+        <v>320</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="56" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
